--- a/1- DOCUMENTOS/1- BASES DE DATOS/3- BB.DD. CARRERAS/BB.DD. CARRERAS.xlsx
+++ b/1- DOCUMENTOS/1- BASES DE DATOS/3- BB.DD. CARRERAS/BB.DD. CARRERAS.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\1- BB.DD. CARRERAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\GITHUB\1- DOCUMENTOS\1- BASES DE DATOS\3- BB.DD. CARRERAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D68FD9-BB42-4C2B-ACBF-65D27750ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{18284660-3B24-4DA8-BF56-23B927E5D51D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,15 +36,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>CARRERAS</t>
+  </si>
+  <si>
+    <t>MEDICINA</t>
+  </si>
+  <si>
+    <t>ENFERMERÍA</t>
+  </si>
+  <si>
+    <t>OBSTETRICIA Y PUERICULTURA</t>
+  </si>
+  <si>
+    <t>KINESIOLOGÍA</t>
+  </si>
+  <si>
+    <t>FONOAUDIOLOGÍA</t>
+  </si>
+  <si>
+    <t>TERAPIA OCUPACIONAL</t>
+  </si>
+  <si>
+    <t>NUTRICIÓN Y DIETÉTICA</t>
+  </si>
+  <si>
+    <t>PSICOLOGÍA</t>
+  </si>
+  <si>
+    <t>ASISTENTE SOCIAL</t>
+  </si>
+  <si>
+    <t>QUÍMICA Y FARMACIA</t>
+  </si>
+  <si>
+    <t>ODONTOLOGÍA</t>
+  </si>
+  <si>
+    <t>BIOQUÍMICA</t>
+  </si>
+  <si>
+    <t>TÉCNICO EN LABORATORIO</t>
+  </si>
+  <si>
+    <t>TÉCNICO EN ALIMENTACIÓN</t>
+  </si>
+  <si>
+    <t>TÉCNICO EN FARMACIA</t>
+  </si>
+  <si>
+    <t>TÉCNICO EN ODONTOLOGÍA NIVEL SUPERIOR</t>
+  </si>
+  <si>
+    <t>TÉCNICO EN ENFERMERÍA NIVEL SUPERIOR</t>
+  </si>
+  <si>
+    <t>TÉCNICO EN ENFERMERÍA NIVEL MEDIO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -391,8 +444,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1BCA1B-B5BD-47E2-A086-F6F86BD42E69}">
-  <dimension ref="F1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="F1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -418,6 +471,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/1- DOCUMENTOS/1- BASES DE DATOS/3- BB.DD. CARRERAS/BB.DD. CARRERAS.xlsx
+++ b/1- DOCUMENTOS/1- BASES DE DATOS/3- BB.DD. CARRERAS/BB.DD. CARRERAS.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\GITHUB\1- DOCUMENTOS\1- BASES DE DATOS\3- BB.DD. CARRERAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\GITHUB\1- DOCUMENTOS\1- BASES DE DATOS\3- BB.DD. CARRERAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F74C4E-EED0-44CD-89AF-55D47D0B1F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,15 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -98,7 +90,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -444,120 +436,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="F1:F19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="7" width="20.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.5703125" customWidth="1"/>
-    <col min="10" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" customWidth="1"/>
-    <col min="12" max="12" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21" customWidth="1"/>
-    <col min="18" max="18" width="22.7109375" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="20" width="32.5703125" customWidth="1"/>
-    <col min="21" max="25" width="21" customWidth="1"/>
+    <col min="1" max="2" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="32.5703125" customWidth="1"/>
+    <col min="16" max="20" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F1" s="1" t="s">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F2" s="1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F3" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F4" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F5" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F6" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F7" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F8" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F9" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F10" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F11" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F12" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F13" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F14" s="1" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F15" s="1" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F16" s="1" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F18" s="1" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
